--- a/job_application_forms/027_sales_engineer_job_application_form--job_application_forms.xlsx
+++ b/job_application_forms/027_sales_engineer_job_application_form--job_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1114,8 +1114,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'jim_doe'}</t>
+          <t>jim_doe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Jim Doe'}</t>
+          <t>Jim Doe</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'1-5_years'}</t>
+          <t>1-5_years</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': '1-5 years'}</t>
+          <t>1-5 years</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'5-10_years'}</t>
+          <t>5-10_years</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': '5-10 years'}</t>
+          <t>5-10 years</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'10+_years'}</t>
+          <t>10+_years</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': '10+ years'}</t>
+          <t>10+ years</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_"bachelor's"}</t>
+          <t>bachelor's</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': "Bachelor's"}</t>
+          <t>Bachelor's</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_"master's"}</t>
+          <t>master's</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': "Master's"}</t>
+          <t>Master's</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'phd'}</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'PhD'}</t>
+          <t>PhD</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'technical'}</t>
+          <t>technical</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Technical'}</t>
+          <t>Technical</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'communication'}</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Communication'}</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'sales_engineer'}</t>
+          <t>sales_engineer</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Sales Engineer'}</t>
+          <t>Sales Engineer</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'software_engineer'}</t>
+          <t>software_engineer</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Software Engineer'}</t>
+          <t>Software Engineer</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'mechanical_engineer'}</t>
+          <t>mechanical_engineer</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Mechanical Engineer'}</t>
+          <t>Mechanical Engineer</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'usa'}</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'USA'}</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'canada'}</t>
+          <t>canada</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Canada'}</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'mexico'}</t>
+          <t>mexico</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Mexico'}</t>
+          <t>Mexico</t>
         </is>
       </c>
     </row>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'full-time'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Full-time'}</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'part-time'}</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Part-time'}</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
@@ -1483,12 +1483,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'remote'}</t>
+          <t>remote</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Remote'}</t>
+          <t>Remote</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1517,12 +1517,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1534,12 +1534,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'onboarding'}</t>
+          <t>onboarding</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Onboarding'}</t>
+          <t>Onboarding</t>
         </is>
       </c>
     </row>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1568,12 +1568,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_specified'}</t>
+          <t>not_specified</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Not Specified'}</t>
+          <t>Not Specified</t>
         </is>
       </c>
     </row>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
